--- a/data/trans_orig/P5704-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5704-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de contar con personas que se preocupan de lo que me sucede en 2007</t>
+          <t>Población según la frecuencia de contar con personas que se preocupan de lo que me sucede en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>334754</t>
+          <t>331241</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>386039</t>
+          <t>383676</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>303655</t>
+          <t>301164</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>354856</t>
+          <t>355347</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>649213</t>
+          <t>654649</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>722899</t>
+          <t>727447</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>203683</t>
+          <t>202035</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>252357</t>
+          <t>251701</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>202593</t>
+          <t>203768</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>248327</t>
+          <t>252372</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>417322</t>
+          <t>411869</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>487770</t>
+          <t>483693</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76419</t>
+          <t>78130</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111742</t>
+          <t>112285</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>75222</t>
+          <t>77819</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>112204</t>
+          <t>112879</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>163474</t>
+          <t>162519</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>213679</t>
+          <t>212490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7794</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24267</t>
+          <t>23859</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25013</t>
+          <t>26016</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47330</t>
+          <t>48768</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37614</t>
+          <t>35979</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66393</t>
+          <t>64271</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15486</t>
+          <t>14073</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15130</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>530041</t>
+          <t>528031</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>591646</t>
+          <t>592022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>522864</t>
+          <t>523742</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>588793</t>
+          <t>589261</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1073357</t>
+          <t>1070975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1157151</t>
+          <t>1159600</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,08%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>239325</t>
+          <t>241380</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>294918</t>
+          <t>300358</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>245299</t>
+          <t>243494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>303897</t>
+          <t>301558</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>500285</t>
+          <t>498159</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>582788</t>
+          <t>583527</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96943</t>
+          <t>96560</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>136975</t>
+          <t>138306</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,49 +1656,49 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>14,38%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>115466</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>94438</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>137893</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>11,92%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
           <t>14,24%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>115466</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>95538</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>136838</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>14,13%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>212</t>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>204207</t>
+          <t>200904</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>261577</t>
+          <t>260522</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>22030</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13507</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33184</t>
+          <t>33609</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24052</t>
+          <t>24521</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48856</t>
+          <t>48317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11714</t>
+          <t>13400</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15923</t>
+          <t>17334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>415197</t>
+          <t>413279</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>463693</t>
+          <t>464471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>403873</t>
+          <t>406948</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>452417</t>
+          <t>456859</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>832546</t>
+          <t>834583</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>906170</t>
+          <t>906130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,51%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>129694</t>
+          <t>127306</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>172565</t>
+          <t>172314</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133571</t>
+          <t>132806</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174155</t>
+          <t>175664</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>275073</t>
+          <t>275093</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>338337</t>
+          <t>333868</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50491</t>
+          <t>50827</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>81799</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>59937</t>
+          <t>60346</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>92969</t>
+          <t>93508</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>118496</t>
+          <t>120594</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>165008</t>
+          <t>168174</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11672</t>
+          <t>12255</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31320</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15628</t>
+          <t>15899</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34300</t>
+          <t>35947</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32496</t>
+          <t>31106</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61501</t>
+          <t>59407</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>981</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10955</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>503641</t>
+          <t>505977</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>562159</t>
+          <t>562730</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>573454</t>
+          <t>569068</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>633235</t>
+          <t>632048</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1091066</t>
+          <t>1090321</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1175788</t>
+          <t>1179491</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,63%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>230003</t>
+          <t>231936</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>284537</t>
+          <t>284109</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>220386</t>
+          <t>218056</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>275377</t>
+          <t>273680</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>470738</t>
+          <t>468510</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>542885</t>
+          <t>546767</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>93417</t>
+          <t>92999</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>130185</t>
+          <t>130322</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>103784</t>
+          <t>104395</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>145035</t>
+          <t>146069</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>207106</t>
+          <t>207226</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>262578</t>
+          <t>263384</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26324</t>
+          <t>26289</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50084</t>
+          <t>50477</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43013</t>
+          <t>44512</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73265</t>
+          <t>75443</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77065</t>
+          <t>77326</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>115151</t>
+          <t>117362</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15077</t>
+          <t>15045</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17363</t>
+          <t>17553</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1833000</t>
+          <t>1834644</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1950440</t>
+          <t>1948459</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1857345</t>
+          <t>1853243</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1973598</t>
+          <t>1969929</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3725020</t>
+          <t>3733187</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3890843</t>
+          <t>3894128</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,53%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>853778</t>
+          <t>855007</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>958173</t>
+          <t>958067</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,82 +3589,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>26,11%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>29,26%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>897641</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>850811</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>952998</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>26,57%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>25,19%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>28,21%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>1770</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1802328</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>1734535</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>1870622</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>27,09%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>26,07%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>29,26%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>897641</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>841274</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>945222</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>24,9%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>27,98%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>1770</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>1802328</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>1728382</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>1870158</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>27,09%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>25,98%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>344181</t>
+          <t>348583</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>425374</t>
+          <t>422460</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>372776</t>
+          <t>369511</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>446818</t>
+          <t>444594</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>742163</t>
+          <t>736502</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>845893</t>
+          <t>843129</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>68818</t>
+          <t>67226</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>104964</t>
+          <t>104532</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>116142</t>
+          <t>115279</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>164159</t>
+          <t>165480</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>193288</t>
+          <t>193783</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>252995</t>
+          <t>251358</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>18691</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>28798</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>17476</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>40192</t>
+          <t>40974</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de contar con personas que se preocupan de lo que me sucede en 2012</t>
+          <t>Población según la frecuencia de contar con personas que se preocupan de lo que me sucede en 2012 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>448395</t>
+          <t>443315</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>497329</t>
+          <t>496640</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>407464</t>
+          <t>408876</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>460565</t>
+          <t>460368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>867419</t>
+          <t>867310</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>938475</t>
+          <t>941947</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>149822</t>
+          <t>149698</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>196372</t>
+          <t>197025</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166346</t>
+          <t>165572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>213805</t>
+          <t>213858</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>331965</t>
+          <t>330472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>398336</t>
+          <t>398358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28827</t>
+          <t>29660</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54134</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37337</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65137</t>
+          <t>65561</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>73068</t>
+          <t>73130</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>110450</t>
+          <t>111872</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>17522</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22458</t>
+          <t>22489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15168</t>
+          <t>15227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33712</t>
+          <t>35610</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17881</t>
+          <t>17201</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>575509</t>
+          <t>571644</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>640224</t>
+          <t>641674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>558533</t>
+          <t>559492</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>625123</t>
+          <t>620880</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1151898</t>
+          <t>1154587</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1246830</t>
+          <t>1244317</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,94%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257411</t>
+          <t>259110</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318100</t>
+          <t>320578</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>290837</t>
+          <t>293138</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>353426</t>
+          <t>354525</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>568291</t>
+          <t>569126</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658630</t>
+          <t>655265</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84373</t>
+          <t>84405</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>124357</t>
+          <t>122712</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>79701</t>
+          <t>80676</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>121030</t>
+          <t>119030</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>175411</t>
+          <t>175882</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>230153</t>
+          <t>228021</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19013</t>
+          <t>17812</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23699</t>
+          <t>23369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35866</t>
+          <t>35980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,82 +5524,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3009</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10312</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>6192</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3009</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>11341</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>6192</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>13440</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>437436</t>
+          <t>437247</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>495696</t>
+          <t>492988</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>422325</t>
+          <t>425812</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>479154</t>
+          <t>481061</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>879004</t>
+          <t>874263</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>960950</t>
+          <t>958087</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,69%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171299</t>
+          <t>171308</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>223552</t>
+          <t>219390</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204704</t>
+          <t>204035</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>256179</t>
+          <t>254622</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>391136</t>
+          <t>382262</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>462998</t>
+          <t>459536</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57772</t>
+          <t>58942</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92193</t>
+          <t>95145</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55797</t>
+          <t>54249</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91201</t>
+          <t>90444</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124605</t>
+          <t>124967</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>173724</t>
+          <t>176298</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20085</t>
+          <t>20235</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12842</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31344</t>
+          <t>30623</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21428</t>
+          <t>21693</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45376</t>
+          <t>45146</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14729</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>514363</t>
+          <t>513132</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>578426</t>
+          <t>575207</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>541269</t>
+          <t>540629</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>606485</t>
+          <t>604094</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1070942</t>
+          <t>1066438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1159957</t>
+          <t>1161048</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,21%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>254740</t>
+          <t>255301</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>314220</t>
+          <t>312622</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,82 +6549,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>33,05%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>336782</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>307968</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>365724</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>32,12%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>29,37%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>34,88%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>619371</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>580770</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>662560</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>31,05%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>29,12%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>33,22%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>336782</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>304405</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>365531</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>32,12%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>29,03%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>34,86%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>619371</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>578760</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>659417</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>31,05%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>29,02%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79287</t>
+          <t>78265</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>117573</t>
+          <t>118163</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>87000</t>
+          <t>85881</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>124853</t>
+          <t>126632</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>172529</t>
+          <t>176862</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>227971</t>
+          <t>230409</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11142</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29606</t>
+          <t>29784</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15612</t>
+          <t>14554</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35510</t>
+          <t>36379</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29945</t>
+          <t>31284</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56477</t>
+          <t>59241</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>984</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8975</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20815</t>
+          <t>19947</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>22977</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2032521</t>
+          <t>2032477</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2150112</t>
+          <t>2158572</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1991998</t>
+          <t>1984897</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2106780</t>
+          <t>2109778</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4054144</t>
+          <t>4054564</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4227669</t>
+          <t>4228541</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,76%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>886985</t>
+          <t>885964</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>990982</t>
+          <t>998077</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1020860</t>
+          <t>1024124</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1133190</t>
+          <t>1138777</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1934495</t>
+          <t>1946647</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2094384</t>
+          <t>2096768</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>283026</t>
+          <t>280807</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>353324</t>
+          <t>354461</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>293673</t>
+          <t>289543</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>366571</t>
+          <t>361716</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>597538</t>
+          <t>591808</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>701973</t>
+          <t>692128</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>36534</t>
+          <t>36721</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>67162</t>
+          <t>66194</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>56477</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>90271</t>
+          <t>89859</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>100485</t>
+          <t>100124</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>146352</t>
+          <t>144080</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7931</t>
+          <t>8380</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>24217</t>
+          <t>25318</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>33624</t>
+          <t>33752</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>24612</t>
+          <t>25953</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>51785</t>
+          <t>53530</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de contar con personas que se preocupan de lo que me sucede en 2016</t>
+          <t>Población según la frecuencia de contar con personas que se preocupan de lo que me sucede en 2016 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>311246</t>
+          <t>313654</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>364979</t>
+          <t>366785</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>300860</t>
+          <t>301854</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>352797</t>
+          <t>352458</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>626875</t>
+          <t>627953</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>702189</t>
+          <t>702281</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>195668</t>
+          <t>197046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>248187</t>
+          <t>244002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>188939</t>
+          <t>189747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>237426</t>
+          <t>237049</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>400180</t>
+          <t>399325</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>469727</t>
+          <t>471366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,11%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80265</t>
+          <t>80628</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117191</t>
+          <t>116900</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>93576</t>
+          <t>90581</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>132041</t>
+          <t>130518</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>184933</t>
+          <t>185249</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>240509</t>
+          <t>238285</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23112</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>21903</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16764</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38088</t>
+          <t>36686</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,77 +8489,77 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6321</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2179</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>12695</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>9947</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>5056</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>19709</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>1,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6321</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2103</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>13592</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>9947</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>5042</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>18015</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>551317</t>
+          <t>547365</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>617501</t>
+          <t>617592</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>555700</t>
+          <t>556512</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>618251</t>
+          <t>621357</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1127767</t>
+          <t>1123993</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1218929</t>
+          <t>1218555</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,06%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276145</t>
+          <t>276071</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>339438</t>
+          <t>334386</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>285551</t>
+          <t>282174</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>344161</t>
+          <t>341479</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>574962</t>
+          <t>579271</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>661617</t>
+          <t>665949</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>90993</t>
+          <t>92264</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>133573</t>
+          <t>132991</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95576</t>
+          <t>95153</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>136344</t>
+          <t>138953</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>198314</t>
+          <t>196290</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>256305</t>
+          <t>257124</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26464</t>
+          <t>27756</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12163</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30437</t>
+          <t>30044</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27420</t>
+          <t>27062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52030</t>
+          <t>51168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>975</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>121</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2237</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16585</t>
+          <t>14854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>326060</t>
+          <t>324797</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>384060</t>
+          <t>382704</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>319032</t>
+          <t>320461</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>375538</t>
+          <t>375643</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>662836</t>
+          <t>662532</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>743698</t>
+          <t>743117</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>233066</t>
+          <t>234372</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>286867</t>
+          <t>288283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>258543</t>
+          <t>258156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>313199</t>
+          <t>312446</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>507473</t>
+          <t>508882</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>584822</t>
+          <t>583896</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,98%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107597</t>
+          <t>107506</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>148985</t>
+          <t>150409</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>114593</t>
+          <t>115575</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158367</t>
+          <t>156504</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>234502</t>
+          <t>235417</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>293623</t>
+          <t>296251</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24695</t>
+          <t>24332</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17804</t>
+          <t>17675</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15950</t>
+          <t>15484</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37182</t>
+          <t>36302</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>518744</t>
+          <t>516890</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>575648</t>
+          <t>577290</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>570881</t>
+          <t>569961</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>637864</t>
+          <t>635297</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1103914</t>
+          <t>1106346</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1192808</t>
+          <t>1193356</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,38%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>237880</t>
+          <t>238599</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>291799</t>
+          <t>295482</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>261976</t>
+          <t>261797</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>324421</t>
+          <t>320044</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>514018</t>
+          <t>515813</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>597411</t>
+          <t>599091</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>85560</t>
+          <t>83584</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>120786</t>
+          <t>120579</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>91257</t>
+          <t>88143</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>130843</t>
+          <t>130551</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>185686</t>
+          <t>184448</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>239922</t>
+          <t>238693</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>11089</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26848</t>
+          <t>26965</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22096</t>
+          <t>20993</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45521</t>
+          <t>44409</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36184</t>
+          <t>35640</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64579</t>
+          <t>64021</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15785</t>
+          <t>16649</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18334</t>
+          <t>18142</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1769409</t>
+          <t>1762067</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1881356</t>
+          <t>1883800</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1805802</t>
+          <t>1803708</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1927188</t>
+          <t>1932582</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3610678</t>
+          <t>3613944</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3770079</t>
+          <t>3774627</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,55%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1003472</t>
+          <t>996473</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1109809</t>
+          <t>1106962</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1044129</t>
+          <t>1039885</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1161582</t>
+          <t>1155891</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2074392</t>
+          <t>2078110</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2229214</t>
+          <t>2230707</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>399425</t>
+          <t>393343</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>479023</t>
+          <t>474751</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>433993</t>
+          <t>432378</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>518907</t>
+          <t>517863</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>850683</t>
+          <t>850440</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>968472</t>
+          <t>968728</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>50086</t>
+          <t>50490</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>82607</t>
+          <t>83905</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>56561</t>
+          <t>56314</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>92423</t>
+          <t>92393</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>114516</t>
+          <t>115862</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>164331</t>
+          <t>162969</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18558</t>
+          <t>18394</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,47 +11212,47 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>19348</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>12370</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>32003</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>19348</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>11656</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>31115</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>19456</t>
+          <t>19869</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>43046</t>
+          <t>44340</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de contar con personas que se preocupan de lo que me sucede en 2023</t>
+          <t>Población según la frecuencia de contar con personas que se preocupan de lo que me sucede en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>352035</t>
+          <t>353378</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>402891</t>
+          <t>404467</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>364417</t>
+          <t>362687</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>403131</t>
+          <t>405199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>731745</t>
+          <t>731888</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>797618</t>
+          <t>799079</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,12%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>153904</t>
+          <t>152321</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>199091</t>
+          <t>197795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>200192</t>
+          <t>197843</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>237823</t>
+          <t>236103</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>363008</t>
+          <t>361386</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>422703</t>
+          <t>423854</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42017</t>
+          <t>42062</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69881</t>
+          <t>67138</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35954</t>
+          <t>36513</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54390</t>
+          <t>55460</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82516</t>
+          <t>83904</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>114711</t>
+          <t>117187</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11026</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26610</t>
+          <t>27811</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>15568</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29323</t>
+          <t>28452</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30097</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49928</t>
+          <t>51560</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13664</t>
+          <t>15424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19998</t>
+          <t>20024</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>646675</t>
+          <t>645951</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>962050</t>
+          <t>995773</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>487722</t>
+          <t>488284</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>540804</t>
+          <t>546636</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1161831</t>
+          <t>1158132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1581921</t>
+          <t>1568317</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>72,96%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>175524</t>
+          <t>161109</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>429946</t>
+          <t>433859</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>293535</t>
+          <t>289471</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>343921</t>
+          <t>339646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>429450</t>
+          <t>432848</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>744915</t>
+          <t>746096</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28460</t>
+          <t>26285</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78128</t>
+          <t>77322</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66836</t>
+          <t>66486</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>97105</t>
+          <t>95174</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>93039</t>
+          <t>92940</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>161776</t>
+          <t>162165</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>10436</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32923</t>
+          <t>32331</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30946</t>
+          <t>30915</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50143</t>
+          <t>50898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12735,7 +12735,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40734</t>
+          <t>40811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76378</t>
+          <t>76721</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>22027</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10472</t>
+          <t>10397</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26957</t>
+          <t>28228</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>380246</t>
+          <t>381128</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>440814</t>
+          <t>440003</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>238953</t>
+          <t>229145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>570544</t>
+          <t>574071</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>567580</t>
+          <t>545216</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>983295</t>
+          <t>978238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,73%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202100</t>
+          <t>200786</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>256561</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>264808</t>
+          <t>260434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>647869</t>
+          <t>669644</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>490547</t>
+          <t>495367</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>968548</t>
+          <t>991740</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>60,55%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36695</t>
+          <t>34631</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63948</t>
+          <t>62998</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29521</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>86677</t>
+          <t>87676</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>72132</t>
+          <t>71851</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>136228</t>
+          <t>134900</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23368</t>
+          <t>23823</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25699</t>
+          <t>25777</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>19014</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44785</t>
+          <t>42631</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>536435</t>
+          <t>537429</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>598264</t>
+          <t>597336</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>652664</t>
+          <t>652551</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>768898</t>
+          <t>771897</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1204177</t>
+          <t>1212316</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1331013</t>
+          <t>1354466</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>232967</t>
+          <t>230050</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>287648</t>
+          <t>284255</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>223708</t>
+          <t>227784</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>315107</t>
+          <t>316393</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>485506</t>
+          <t>473206</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>587380</t>
+          <t>581362</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>45854</t>
+          <t>46597</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>75021</t>
+          <t>74486</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51526</t>
+          <t>50562</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>80215</t>
+          <t>81576</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>105300</t>
+          <t>105520</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>145627</t>
+          <t>150256</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24264</t>
+          <t>24687</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46114</t>
+          <t>44816</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28775</t>
+          <t>29072</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50524</t>
+          <t>50802</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>58946</t>
+          <t>58142</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>88474</t>
+          <t>89532</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16380</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18341</t>
+          <t>18161</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,47 +14207,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>20641</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>13979</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>28782</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>20641</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>13839</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2000535</t>
+          <t>2006632</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2399977</t>
+          <t>2414043</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1656870</t>
+          <t>1620813</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2172856</t>
+          <t>2178507</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3772504</t>
+          <t>3761732</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4426979</t>
+          <t>4428582</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,28%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>787695</t>
+          <t>781985</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1096001</t>
+          <t>1090906</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1071361</t>
+          <t>1065537</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1697645</t>
+          <t>1706786</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2007140</t>
+          <t>2010104</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2756347</t>
+          <t>2734520</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>171522</t>
+          <t>170449</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>251090</t>
+          <t>251540</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>204697</t>
+          <t>205506</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>282906</t>
+          <t>284261</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,47 +14663,47 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>467086</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>398405</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>513766</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>5,6%</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>467086</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>406912</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>518099</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>68338</t>
+          <t>66818</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>110154</t>
+          <t>107778</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>94675</t>
+          <t>90503</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>136831</t>
+          <t>134898</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>174984</t>
+          <t>171252</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>234241</t>
+          <t>235266</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>20564</t>
+          <t>20239</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>41607</t>
+          <t>41089</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>19896</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>36752</t>
+          <t>36166</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>44571</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>72625</t>
+          <t>72762</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">

--- a/data/trans_orig/P5704-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5704-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>331241</t>
+          <t>331031</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>383676</t>
+          <t>384142</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>301164</t>
+          <t>305237</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>355347</t>
+          <t>354577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>654649</t>
+          <t>650572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>727447</t>
+          <t>723039</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,3%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>202035</t>
+          <t>202416</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>251701</t>
+          <t>251786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>203768</t>
+          <t>201055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252372</t>
+          <t>250683</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>411869</t>
+          <t>419009</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>483693</t>
+          <t>487056</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78130</t>
+          <t>75539</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112285</t>
+          <t>111119</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77819</t>
+          <t>74671</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>112879</t>
+          <t>110716</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>162519</t>
+          <t>161212</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>211047</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23859</t>
+          <t>24150</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26016</t>
+          <t>24200</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48768</t>
+          <t>47084</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35979</t>
+          <t>37671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64271</t>
+          <t>66224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14073</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>14390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>528031</t>
+          <t>529762</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>592022</t>
+          <t>592011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>523742</t>
+          <t>525564</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>589261</t>
+          <t>585978</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1070975</t>
+          <t>1072414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1159600</t>
+          <t>1160955</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,15%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>241380</t>
+          <t>238362</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>300358</t>
+          <t>293681</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>243494</t>
+          <t>245763</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>301558</t>
+          <t>301269</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>498159</t>
+          <t>502945</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>583527</t>
+          <t>585647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96560</t>
+          <t>95841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>138306</t>
+          <t>137431</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94438</t>
+          <t>96097</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>137893</t>
+          <t>136695</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>200904</t>
+          <t>201938</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>260522</t>
+          <t>261913</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22030</t>
+          <t>21925</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>13227</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33609</t>
+          <t>31868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24521</t>
+          <t>23658</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48317</t>
+          <t>47365</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13400</t>
+          <t>12135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>413279</t>
+          <t>412792</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>464471</t>
+          <t>464532</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>406948</t>
+          <t>405369</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>456859</t>
+          <t>453244</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>834583</t>
+          <t>833010</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>906130</t>
+          <t>905186</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,44%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127306</t>
+          <t>132536</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>172314</t>
+          <t>176573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132806</t>
+          <t>132666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175664</t>
+          <t>175405</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>275093</t>
+          <t>274594</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>333868</t>
+          <t>339421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50827</t>
+          <t>50828</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81799</t>
+          <t>82499</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>60346</t>
+          <t>59923</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>93508</t>
+          <t>92365</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120594</t>
+          <t>120435</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>168174</t>
+          <t>165800</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12255</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31417</t>
+          <t>31338</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15899</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35947</t>
+          <t>35550</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31106</t>
+          <t>32209</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59407</t>
+          <t>60283</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>986</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>11141</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>505977</t>
+          <t>502791</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>562730</t>
+          <t>560380</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>569068</t>
+          <t>571840</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>632048</t>
+          <t>635650</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1090321</t>
+          <t>1089118</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1179491</t>
+          <t>1176855</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,49%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>231936</t>
+          <t>234557</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>284109</t>
+          <t>288216</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>218056</t>
+          <t>218839</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>273680</t>
+          <t>274083</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>468510</t>
+          <t>468846</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>546767</t>
+          <t>544894</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>92999</t>
+          <t>93669</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>130322</t>
+          <t>131021</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>104395</t>
+          <t>104761</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>146069</t>
+          <t>146078</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>207226</t>
+          <t>204825</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>263384</t>
+          <t>261634</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26289</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50477</t>
+          <t>50178</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44512</t>
+          <t>45482</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75443</t>
+          <t>76546</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77326</t>
+          <t>75668</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>117362</t>
+          <t>115659</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15045</t>
+          <t>15051</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>17313</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1834644</t>
+          <t>1834102</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1948459</t>
+          <t>1944261</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1853243</t>
+          <t>1856356</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1969929</t>
+          <t>1976301</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3733187</t>
+          <t>3720363</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3894128</t>
+          <t>3886313</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,41%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>855007</t>
+          <t>853976</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>958067</t>
+          <t>955436</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>850811</t>
+          <t>850041</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>952998</t>
+          <t>951404</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1734535</t>
+          <t>1728671</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1870622</t>
+          <t>1878094</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>348583</t>
+          <t>350565</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>422460</t>
+          <t>420888</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>369511</t>
+          <t>370556</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>444594</t>
+          <t>447564</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>736502</t>
+          <t>739457</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>843129</t>
+          <t>846262</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>67226</t>
+          <t>67105</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>104532</t>
+          <t>104930</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>115279</t>
+          <t>118148</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>165480</t>
+          <t>165552</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>193783</t>
+          <t>196574</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>251358</t>
+          <t>257301</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18691</t>
+          <t>19162</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>10515</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28798</t>
+          <t>28374</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17476</t>
+          <t>18582</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>40974</t>
+          <t>40180</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>443315</t>
+          <t>447252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>496640</t>
+          <t>496853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>408876</t>
+          <t>404503</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>460368</t>
+          <t>459460</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>867310</t>
+          <t>867368</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>941947</t>
+          <t>943040</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,6%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>149698</t>
+          <t>151819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>197025</t>
+          <t>196921</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>165572</t>
+          <t>167108</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>213858</t>
+          <t>215470</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>330472</t>
+          <t>332583</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>398358</t>
+          <t>397466</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29660</t>
+          <t>29512</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>54460</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>37495</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65561</t>
+          <t>66079</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>73130</t>
+          <t>73556</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>111872</t>
+          <t>113094</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17522</t>
+          <t>18014</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>7572</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22489</t>
+          <t>22173</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15227</t>
+          <t>15239</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35610</t>
+          <t>34181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8925</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13509</t>
+          <t>13669</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17201</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>571644</t>
+          <t>572580</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>641674</t>
+          <t>637647</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>559492</t>
+          <t>555733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>620880</t>
+          <t>623623</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1154587</t>
+          <t>1154059</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1244317</t>
+          <t>1248858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,16%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>259110</t>
+          <t>261770</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320578</t>
+          <t>320650</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>293138</t>
+          <t>291283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>354525</t>
+          <t>353514</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>569126</t>
+          <t>569470</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>655265</t>
+          <t>658063</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84405</t>
+          <t>84516</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122712</t>
+          <t>124293</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80676</t>
+          <t>78399</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>119030</t>
+          <t>121108</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>175882</t>
+          <t>175313</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>228021</t>
+          <t>230107</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17812</t>
+          <t>19682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23369</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13968</t>
+          <t>15032</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35980</t>
+          <t>37300</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10312</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>14460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>437247</t>
+          <t>434217</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>492988</t>
+          <t>492391</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>425812</t>
+          <t>423826</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>481061</t>
+          <t>480583</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>874263</t>
+          <t>875427</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>958087</t>
+          <t>955490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,52%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171308</t>
+          <t>169305</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>219390</t>
+          <t>220556</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204035</t>
+          <t>203683</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254622</t>
+          <t>255743</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>382262</t>
+          <t>386952</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>459536</t>
+          <t>460713</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58942</t>
+          <t>58901</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>95145</t>
+          <t>96171</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54249</t>
+          <t>57199</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90444</t>
+          <t>91058</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124967</t>
+          <t>122571</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>176298</t>
+          <t>174764</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5413</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20235</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>12682</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30623</t>
+          <t>31043</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>21504</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45146</t>
+          <t>46596</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12365</t>
+          <t>12300</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>16229</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>513132</t>
+          <t>514158</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>575207</t>
+          <t>577658</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>540629</t>
+          <t>538633</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>604094</t>
+          <t>603739</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1066438</t>
+          <t>1069775</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1161048</t>
+          <t>1162741</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,3%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>255301</t>
+          <t>250858</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312622</t>
+          <t>312455</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>307968</t>
+          <t>309645</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>365724</t>
+          <t>368850</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>580770</t>
+          <t>574975</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>662560</t>
+          <t>662227</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>78265</t>
+          <t>76844</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118163</t>
+          <t>115749</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>85881</t>
+          <t>86026</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>126632</t>
+          <t>125612</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>176862</t>
+          <t>174880</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>230409</t>
+          <t>230431</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11004</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29784</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36379</t>
+          <t>34965</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31284</t>
+          <t>29806</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59241</t>
+          <t>56246</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>979</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19947</t>
+          <t>20155</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22977</t>
+          <t>22616</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2032477</t>
+          <t>2035509</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2158572</t>
+          <t>2148098</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1984897</t>
+          <t>1988757</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2109778</t>
+          <t>2112208</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4054564</t>
+          <t>4055627</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4228541</t>
+          <t>4217275</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,59%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>885964</t>
+          <t>884871</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>998077</t>
+          <t>991426</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1024124</t>
+          <t>1022666</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1138777</t>
+          <t>1135581</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1946647</t>
+          <t>1941395</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2096768</t>
+          <t>2097417</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>280807</t>
+          <t>282699</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>354461</t>
+          <t>353101</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>289543</t>
+          <t>290601</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>361716</t>
+          <t>367129</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>591808</t>
+          <t>592022</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>692128</t>
+          <t>687977</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>36721</t>
+          <t>36748</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>66194</t>
+          <t>66314</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>56477</t>
+          <t>55723</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>89859</t>
+          <t>90541</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>100124</t>
+          <t>97503</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>144080</t>
+          <t>147638</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>25318</t>
+          <t>24029</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>14091</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>33752</t>
+          <t>34214</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,47 +7605,47 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>37598</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>26537</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>52701</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>37598</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>25953</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>53530</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>313654</t>
+          <t>312435</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>366785</t>
+          <t>364010</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>301854</t>
+          <t>297495</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>352458</t>
+          <t>352507</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>627953</t>
+          <t>628990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>702281</t>
+          <t>702561</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>197046</t>
+          <t>197907</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244002</t>
+          <t>243872</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>189747</t>
+          <t>190504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>237049</t>
+          <t>236888</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>399325</t>
+          <t>397278</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>471366</t>
+          <t>469076</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80628</t>
+          <t>80038</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>116900</t>
+          <t>118398</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90581</t>
+          <t>94804</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>130518</t>
+          <t>134867</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>185249</t>
+          <t>184825</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>238285</t>
+          <t>237581</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22707</t>
+          <t>22888</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21903</t>
+          <t>21926</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36686</t>
+          <t>37805</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10998</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>18816</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>547365</t>
+          <t>551633</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>617592</t>
+          <t>615583</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>556512</t>
+          <t>554913</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>621357</t>
+          <t>625520</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1123993</t>
+          <t>1125513</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1218555</t>
+          <t>1218353</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,05%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276071</t>
+          <t>274031</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>334386</t>
+          <t>335010</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>282174</t>
+          <t>283460</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341479</t>
+          <t>344924</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>579271</t>
+          <t>573845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>665949</t>
+          <t>660767</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92264</t>
+          <t>93127</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>132991</t>
+          <t>136659</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95153</t>
+          <t>94516</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>138953</t>
+          <t>136696</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>196290</t>
+          <t>199943</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>257124</t>
+          <t>260521</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>10998</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27756</t>
+          <t>27379</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>12216</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30044</t>
+          <t>30729</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27062</t>
+          <t>27279</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51168</t>
+          <t>51864</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>10560</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14854</t>
+          <t>14674</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>324797</t>
+          <t>327335</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>382704</t>
+          <t>387926</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>320461</t>
+          <t>321535</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>375643</t>
+          <t>378788</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>662532</t>
+          <t>664863</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>743117</t>
+          <t>745545</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,5%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>234372</t>
+          <t>232339</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>288283</t>
+          <t>285838</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>258156</t>
+          <t>259739</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>312446</t>
+          <t>315997</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>508882</t>
+          <t>506880</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>583896</t>
+          <t>579427</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107506</t>
+          <t>106271</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>150409</t>
+          <t>148429</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>115575</t>
+          <t>113853</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>156504</t>
+          <t>159733</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>235417</t>
+          <t>236046</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>296251</t>
+          <t>294217</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8523</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24332</t>
+          <t>24209</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>15199</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36302</t>
+          <t>36004</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>516890</t>
+          <t>519696</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>577290</t>
+          <t>577458</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>569961</t>
+          <t>570963</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>635297</t>
+          <t>634523</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1106346</t>
+          <t>1106096</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1193356</t>
+          <t>1195895</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,51%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>238599</t>
+          <t>238286</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>295482</t>
+          <t>293041</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>261797</t>
+          <t>263064</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>320044</t>
+          <t>322430</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>515813</t>
+          <t>512525</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>599091</t>
+          <t>595340</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83584</t>
+          <t>83728</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>120579</t>
+          <t>119834</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>88143</t>
+          <t>87631</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>130551</t>
+          <t>131150</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>184448</t>
+          <t>182725</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>238693</t>
+          <t>239068</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26965</t>
+          <t>27245</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20993</t>
+          <t>20816</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44409</t>
+          <t>43332</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35640</t>
+          <t>37564</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64021</t>
+          <t>64151</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>7742</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16649</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18142</t>
+          <t>18689</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1762067</t>
+          <t>1772116</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1883800</t>
+          <t>1885824</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1803708</t>
+          <t>1800249</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1932582</t>
+          <t>1922141</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3613944</t>
+          <t>3609765</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3774627</t>
+          <t>3778394</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,6%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>996473</t>
+          <t>995459</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1106962</t>
+          <t>1106350</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1039885</t>
+          <t>1046618</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1155891</t>
+          <t>1158619</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2078110</t>
+          <t>2082543</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2230707</t>
+          <t>2238365</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>393343</t>
+          <t>398008</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>474751</t>
+          <t>477723</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>432378</t>
+          <t>435120</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>517863</t>
+          <t>516082</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>850440</t>
+          <t>855230</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>968728</t>
+          <t>967568</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>50490</t>
+          <t>49380</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>83905</t>
+          <t>81061</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>56314</t>
+          <t>56228</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>92393</t>
+          <t>91122</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>115862</t>
+          <t>113280</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>162969</t>
+          <t>160483</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12370</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>32003</t>
+          <t>29999</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>19869</t>
+          <t>19433</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>44340</t>
+          <t>42419</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -11654,32 +11654,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>379491</t>
+          <t>402209</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>353378</t>
+          <t>372650</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>404467</t>
+          <t>430392</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,32 +11689,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>384433</t>
+          <t>413657</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>362687</t>
+          <t>390409</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>405199</t>
+          <t>434519</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>763924</t>
+          <t>815865</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>731888</t>
+          <t>781055</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>799079</t>
+          <t>852061</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,01%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>174942</t>
+          <t>197374</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152321</t>
+          <t>172778</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>197795</t>
+          <t>220744</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>217512</t>
+          <t>237824</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>197843</t>
+          <t>218084</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>236103</t>
+          <t>258466</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>392454</t>
+          <t>435198</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>361386</t>
+          <t>404364</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>423854</t>
+          <t>469955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53764</t>
+          <t>58950</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42062</t>
+          <t>44628</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67138</t>
+          <t>73934</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44581</t>
+          <t>48034</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36513</t>
+          <t>38620</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55460</t>
+          <t>59371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>98345</t>
+          <t>106984</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83904</t>
+          <t>90489</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>117187</t>
+          <t>125877</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17856</t>
+          <t>21913</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11914</t>
+          <t>13879</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27811</t>
+          <t>33433</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>24257</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>17799</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28452</t>
+          <t>32318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>39226</t>
+          <t>46170</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30097</t>
+          <t>35602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51560</t>
+          <t>59210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15424</t>
+          <t>16413</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>11706</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>13522</t>
+          <t>15683</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20024</t>
+          <t>22952</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>634075</t>
+          <t>689363</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>634075</t>
+          <t>689363</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>634075</t>
+          <t>689363</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>673396</t>
+          <t>730538</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>673396</t>
+          <t>730538</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>673396</t>
+          <t>730538</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1307471</t>
+          <t>1419901</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1307471</t>
+          <t>1419901</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1307471</t>
+          <t>1419901</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>769921</t>
+          <t>574369</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>645951</t>
+          <t>535848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>995773</t>
+          <t>610191</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>516153</t>
+          <t>564310</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>488284</t>
+          <t>536860</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>546636</t>
+          <t>592966</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1286075</t>
+          <t>1138679</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1158132</t>
+          <t>1090930</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1568317</t>
+          <t>1183828</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>55,93%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>332561</t>
+          <t>363169</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>161109</t>
+          <t>331501</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>433859</t>
+          <t>398816</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>315779</t>
+          <t>359906</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>289471</t>
+          <t>334211</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>339646</t>
+          <t>387563</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>648340</t>
+          <t>723075</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>432848</t>
+          <t>682651</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>746096</t>
+          <t>770402</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56905</t>
+          <t>66992</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26285</t>
+          <t>53042</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77322</t>
+          <t>82587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>79525</t>
+          <t>90652</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66486</t>
+          <t>76096</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95174</t>
+          <t>106903</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>136430</t>
+          <t>157644</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>92940</t>
+          <t>135584</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>162165</t>
+          <t>180581</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>29704</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>21365</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32331</t>
+          <t>42717</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39667</t>
+          <t>47724</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30915</t>
+          <t>37428</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50898</t>
+          <t>59607</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>61028</t>
+          <t>77429</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40811</t>
+          <t>63578</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76721</t>
+          <t>94114</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11953</t>
+          <t>12814</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22027</t>
+          <t>22153</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,67 +12823,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10175</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>19900</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>12913</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>29491</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>17820</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>10397</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>28228</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1192702</t>
+          <t>1047048</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1192702</t>
+          <t>1047048</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1192702</t>
+          <t>1047048</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>956991</t>
+          <t>1069677</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>956991</t>
+          <t>1069677</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>956991</t>
+          <t>1069677</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2149693</t>
+          <t>2116726</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2149693</t>
+          <t>2116726</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2149693</t>
+          <t>2116726</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>410460</t>
+          <t>450442</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>381128</t>
+          <t>419505</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>440003</t>
+          <t>482823</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,27 +13053,27 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>435287</t>
+          <t>472707</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>229145</t>
+          <t>447104</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>574071</t>
+          <t>499583</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>845747</t>
+          <t>923149</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>545216</t>
+          <t>882783</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>978238</t>
+          <t>966123</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,85%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>229296</t>
+          <t>262933</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>200786</t>
+          <t>233488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>256561</t>
+          <t>294482</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>418065</t>
+          <t>245616</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>260434</t>
+          <t>220958</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>669644</t>
+          <t>270389</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>647361</t>
+          <t>508549</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>495367</t>
+          <t>471003</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>991740</t>
+          <t>548488</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>48143</t>
+          <t>62720</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34631</t>
+          <t>47082</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62998</t>
+          <t>81557</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59085</t>
+          <t>66982</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>52723</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87676</t>
+          <t>85275</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>107228</t>
+          <t>129702</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>71851</t>
+          <t>106301</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>134900</t>
+          <t>155771</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>24199</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>15408</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23823</t>
+          <t>41673</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>20233</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25777</t>
+          <t>29005</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>32133</t>
+          <t>44432</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19014</t>
+          <t>33024</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42631</t>
+          <t>61489</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>8321</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10653</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>565044</t>
+          <t>590887</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>537429</t>
+          <t>554899</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>597336</t>
+          <t>621937</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>693148</t>
+          <t>668052</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>652551</t>
+          <t>639153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>771897</t>
+          <t>696190</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1258191</t>
+          <t>1258939</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1212316</t>
+          <t>1217277</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1354466</t>
+          <t>1301262</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>258043</t>
+          <t>282201</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>230050</t>
+          <t>255605</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>284255</t>
+          <t>314402</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>281897</t>
+          <t>312106</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>227784</t>
+          <t>287430</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>316393</t>
+          <t>339532</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>539940</t>
+          <t>594307</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>473206</t>
+          <t>555405</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>581362</t>
+          <t>632585</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>59204</t>
+          <t>66197</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46597</t>
+          <t>52442</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>74486</t>
+          <t>83186</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>65879</t>
+          <t>72346</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50562</t>
+          <t>59490</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>81576</t>
+          <t>88183</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>125084</t>
+          <t>138543</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>105520</t>
+          <t>119647</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>150256</t>
+          <t>159694</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>33683</t>
+          <t>37601</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24687</t>
+          <t>28107</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44816</t>
+          <t>51659</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>38281</t>
+          <t>45988</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29072</t>
+          <t>35441</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50802</t>
+          <t>58538</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>71963</t>
+          <t>83589</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>58142</t>
+          <t>69540</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>89532</t>
+          <t>101290</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>11138</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15670</t>
+          <t>19558</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11977</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>10382</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18161</t>
+          <t>23912</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>20641</t>
+          <t>26965</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13979</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28782</t>
+          <t>37889</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>924639</t>
+          <t>988023</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>924639</t>
+          <t>988023</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>924639</t>
+          <t>988023</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1091181</t>
+          <t>1114319</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1091181</t>
+          <t>1114319</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1091181</t>
+          <t>1114319</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2015820</t>
+          <t>2102342</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2015820</t>
+          <t>2102342</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2015820</t>
+          <t>2102342</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2124917</t>
+          <t>2017906</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2006632</t>
+          <t>1951367</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2414043</t>
+          <t>2079088</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2029021</t>
+          <t>2118726</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1620813</t>
+          <t>2064069</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2178507</t>
+          <t>2171948</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4153938</t>
+          <t>4136631</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3761732</t>
+          <t>4047928</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4428582</t>
+          <t>4221135</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>58,2%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>994842</t>
+          <t>1105677</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>781985</t>
+          <t>1046079</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1090906</t>
+          <t>1169232</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1233253</t>
+          <t>1155452</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1065537</t>
+          <t>1109405</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1706786</t>
+          <t>1210757</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2228095</t>
+          <t>2261129</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2010104</t>
+          <t>2183504</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2734520</t>
+          <t>2334014</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>218016</t>
+          <t>254859</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>170449</t>
+          <t>224933</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>251540</t>
+          <t>286706</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>249070</t>
+          <t>278014</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>205506</t>
+          <t>250318</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>284261</t>
+          <t>305931</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>467086</t>
+          <t>532873</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>398405</t>
+          <t>488866</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>513766</t>
+          <t>576253</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>88151</t>
+          <t>113417</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>66818</t>
+          <t>95677</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>107778</t>
+          <t>137332</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>116200</t>
+          <t>138203</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>90503</t>
+          <t>119864</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>134898</t>
+          <t>156701</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>204351</t>
+          <t>251620</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>171252</t>
+          <t>224793</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>235266</t>
+          <t>282209</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>30005</t>
+          <t>34469</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>20239</t>
+          <t>25154</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>41089</t>
+          <t>49651</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>27390</t>
+          <t>36399</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19896</t>
+          <t>27274</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>36166</t>
+          <t>48837</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>57395</t>
+          <t>70869</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>44571</t>
+          <t>57410</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>72762</t>
+          <t>88386</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3455931</t>
+          <t>3526328</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3455931</t>
+          <t>3526328</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3455931</t>
+          <t>3526328</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3654933</t>
+          <t>3726794</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3654933</t>
+          <t>3726794</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3654933</t>
+          <t>3726794</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7110865</t>
+          <t>7253122</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7110865</t>
+          <t>7253122</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7110865</t>
+          <t>7253122</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
